--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>公共管理学</t>
   </si>
@@ -38,610 +38,49 @@
     <t>供量/余量</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>福建农林大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 619</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 848</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共政策学 预测卷（一）</t>
-    </r>
+    <t>福建农林大学 619公共管理学 &amp; 848公共政策学 预测卷（一）</t>
   </si>
   <si>
     <t>5（5）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>广西大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 614</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 809</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>社会研究方法 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>华东理工大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 623</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">社会科学研究方法 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 828</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理综合（行政管理） 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>华东理工大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 623</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">社会科学研究方法 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 828</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理综合（社会保障） 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>华南理工大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 626</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理基础与前沿 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 829</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理研究方法 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>华南师范大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 619</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 840</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>社会科学研究方法 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>南京大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 661</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理基础 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 810</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共政策 预测卷（二）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>四川大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 666</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学科基础知识 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 814</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理学 预测卷（二）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>武汉大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共管理研究方法 预测卷（二）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>西南财经大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 633</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学基础 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 803</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理学 预测卷（一）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>浙江财经大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 611</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">公共管理学 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 812</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公共政策学 预测卷（一）</t>
-    </r>
+    <t>广西大学 614公共管理学 &amp; 809社会研究方法 预测卷（一）</t>
+  </si>
+  <si>
+    <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（社会保障） 预测卷（一）</t>
+  </si>
+  <si>
+    <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（行政管理） 预测卷（一）</t>
+  </si>
+  <si>
+    <t>华南理工大学 626公共管理基础与前沿 &amp; 829公共管理研究方法 预测卷（一）</t>
+  </si>
+  <si>
+    <t>华南师范大学 619公共管理学 &amp; 840社会科学研究方法 预测卷（一）</t>
+  </si>
+  <si>
+    <t>华中师范大学 709公共管理学 &amp; 820公共管理研究方法 预测卷（一）</t>
+  </si>
+  <si>
+    <t>南京大学 661公共管理基础 &amp; 810公共政策 预测卷（二）</t>
+  </si>
+  <si>
+    <t>四川大学 666公共管理学科基础知识 &amp; 814公共管理学 预测卷（二）</t>
+  </si>
+  <si>
+    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷（二）</t>
+  </si>
+  <si>
+    <t>西南财经大学 633公共管理学基础 &amp; 803管理学 预测卷（一）</t>
+  </si>
+  <si>
+    <t>浙江财经大学 611公共管理学 &amp; 812公共政策学 预测卷（一）</t>
   </si>
   <si>
     <t>社会学</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>四川大学</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 664</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">社会学综合 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&amp; 813</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>社会学理论与方法 预测卷（一）</t>
-    </r>
+    <t>四川大学 664社会学综合 &amp; 813社会学理论与方法 预测卷（一）</t>
   </si>
 </sst>
 </file>
@@ -654,7 +93,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -812,12 +251,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1270,17 +703,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1818,160 +1254,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="B2:B13">
+    <sortCondition ref="B2"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
   <si>
     <t>公共管理学</t>
   </si>
@@ -38,10 +38,13 @@
     <t>供量/余量</t>
   </si>
   <si>
+    <t>电子科技大学 631公共管理 &amp; 864公共政策 预测卷（一）</t>
+  </si>
+  <si>
+    <t>5（5）</t>
+  </si>
+  <si>
     <t>福建农林大学 619公共管理学 &amp; 848公共政策学 预测卷（一）</t>
-  </si>
-  <si>
-    <t>5（5）</t>
   </si>
   <si>
     <t>广西大学 614公共管理学 &amp; 809社会研究方法 预测卷（一）</t>
@@ -713,10 +716,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1244,7 +1247,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
@@ -1268,10 +1271,10 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1279,10 +1282,10 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1290,10 +1293,10 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1301,10 +1304,10 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1312,10 +1315,10 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1323,10 +1326,10 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1334,10 +1337,10 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1345,10 +1348,10 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1356,10 +1359,10 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1367,10 +1370,10 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1378,10 +1381,10 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1389,37 +1392,46 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2">
+    <row r="16" spans="1:3">
+      <c r="A16" s="2">
         <v>1</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B2:B13">
+  <sortState ref="B2:B14">
     <sortCondition ref="B2"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
   <si>
     <t>公共管理学</t>
   </si>
@@ -1406,7 +1406,9 @@
       <c r="B14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>公共管理学</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（社会保障） 预测卷（一）</t>
+  </si>
+  <si>
+    <t>5（4）</t>
   </si>
   <si>
     <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（行政管理） 预测卷（一）</t>
@@ -706,21 +709,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1251,184 +1260,184 @@
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
-    <col min="2" max="2" width="86.0576923076923" style="1" customWidth="1"/>
+    <col min="2" max="2" width="86.0576923076923" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.5384615384615" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="B10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2">
+    <row r="12" spans="1:3">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -1383,7 +1383,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3">

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>公共管理学</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷（二）</t>
+  </si>
+  <si>
+    <t>5（3）</t>
   </si>
   <si>
     <t>西南财经大学 633公共管理学基础 &amp; 803管理学 预测卷（一）</t>
@@ -1394,7 +1397,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1402,7 +1405,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>4</v>
@@ -1413,7 +1416,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>4</v>
@@ -1421,7 +1424,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>1</v>
@@ -1435,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -74,10 +74,10 @@
     <t>四川大学 666公共管理学科基础知识 &amp; 814公共管理学 预测卷（二）</t>
   </si>
   <si>
+    <t>5（3）</t>
+  </si>
+  <si>
     <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷（二）</t>
-  </si>
-  <si>
-    <t>5（3）</t>
   </si>
   <si>
     <t>西南财经大学 633公共管理学基础 &amp; 803管理学 预测卷（一）</t>
@@ -1386,7 +1386,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1394,10 +1394,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3">

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22480" windowHeight="17120"/>
+    <workbookView windowWidth="22840" windowHeight="17120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,19 +41,19 @@
     <t>电子科技大学 631公共管理 &amp; 864公共政策 预测卷（一）</t>
   </si>
   <si>
+    <t>5（4）</t>
+  </si>
+  <si>
+    <t>福建农林大学 619公共管理学 &amp; 848公共政策学 预测卷（一）</t>
+  </si>
+  <si>
     <t>5（5）</t>
   </si>
   <si>
-    <t>福建农林大学 619公共管理学 &amp; 848公共政策学 预测卷（一）</t>
-  </si>
-  <si>
     <t>广西大学 614公共管理学 &amp; 809社会研究方法 预测卷（一）</t>
   </si>
   <si>
     <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（社会保障） 预测卷（一）</t>
-  </si>
-  <si>
-    <t>5（4）</t>
   </si>
   <si>
     <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（行政管理） 预测卷（一）</t>
@@ -1298,7 +1298,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1306,10 +1306,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1317,10 +1317,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1331,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1342,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1397,7 +1397,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1408,7 +1408,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1419,7 +1419,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1441,7 +1441,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -1,270 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22840" windowHeight="17120"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
-  <si>
-    <t>公共管理学</t>
-  </si>
-  <si>
-    <t>预测卷</t>
-  </si>
-  <si>
-    <t>供量/余量</t>
-  </si>
-  <si>
-    <t>电子科技大学 631公共管理 &amp; 864公共政策 预测卷（一）</t>
-  </si>
-  <si>
-    <t>5（4）</t>
-  </si>
-  <si>
-    <t>福建农林大学 619公共管理学 &amp; 848公共政策学 预测卷（一）</t>
-  </si>
-  <si>
-    <t>5（5）</t>
-  </si>
-  <si>
-    <t>广西大学 614公共管理学 &amp; 809社会研究方法 预测卷（一）</t>
-  </si>
-  <si>
-    <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（社会保障） 预测卷（一）</t>
-  </si>
-  <si>
-    <t>华东理工大学 623社会科学研究方法 &amp; 828公共管理综合（行政管理） 预测卷（一）</t>
-  </si>
-  <si>
-    <t>华南理工大学 626公共管理基础与前沿 &amp; 829公共管理研究方法 预测卷（一）</t>
-  </si>
-  <si>
-    <t>华南师范大学 619公共管理学 &amp; 840社会科学研究方法 预测卷（一）</t>
-  </si>
-  <si>
-    <t>华中师范大学 709公共管理学 &amp; 820公共管理研究方法 预测卷（一）</t>
-  </si>
-  <si>
-    <t>南京大学 661公共管理基础 &amp; 810公共政策 预测卷（二）</t>
-  </si>
-  <si>
-    <t>四川大学 666公共管理学科基础知识 &amp; 814公共管理学 预测卷（二）</t>
-  </si>
-  <si>
-    <t>5（3）</t>
-  </si>
-  <si>
-    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷（二）</t>
-  </si>
-  <si>
-    <t>西南财经大学 633公共管理学基础 &amp; 803管理学 预测卷（一）</t>
-  </si>
-  <si>
-    <t>浙江财经大学 611公共管理学 &amp; 812公共政策学 预测卷（一）</t>
-  </si>
-  <si>
-    <t>社会学</t>
-  </si>
-  <si>
-    <t>四川大学 664社会学综合 &amp; 813社会学理论与方法 预测卷（一）</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="10.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -564,174 +478,174 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -979,7 +893,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -988,7 +902,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1001,11 +915,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1257,198 +1234,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
-    <col min="2" max="2" width="86.0576923076923" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.5384615384615" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.23076923076923" style="1"/>
+    <col width="12.7692307692308" customWidth="1" style="3" min="1" max="1"/>
+    <col width="86.05769230769231" customWidth="1" style="4" min="2" max="2"/>
+    <col width="11.5384615384615" customWidth="1" style="3" min="3" max="3"/>
+    <col width="9.23076923076923" customWidth="1" style="3" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>公共管理学</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>预测卷</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>供量/余量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>5（5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>广西大学 614 &amp; 809 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>5（5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>南京大学 661 &amp; 810 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>四川大学 666 &amp; 814 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>5（3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>5（4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>5（5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>5（5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>社会学</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>预测卷</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>供量/余量</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="3">
-        <v>1</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>15</v>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>四川大学 664 &amp; 813 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>5（3）</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B2:B14">
-    <sortCondition ref="B2"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -1,184 +1,270 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="26940" windowHeight="17120"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+  <si>
+    <t>公共管理学</t>
+  </si>
+  <si>
+    <t>预测卷</t>
+  </si>
+  <si>
+    <t>供量/余量</t>
+  </si>
+  <si>
+    <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
+  </si>
+  <si>
+    <t>5（4）</t>
+  </si>
+  <si>
+    <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
+  </si>
+  <si>
+    <t>5（5）</t>
+  </si>
+  <si>
+    <t>广西大学 614 &amp; 809 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
+  </si>
+  <si>
+    <t>5（3）</t>
+  </si>
+  <si>
+    <t>南京大学 661 &amp; 810 预测卷(二)</t>
+  </si>
+  <si>
+    <t>四川大学 666 &amp; 814 预测卷(二)</t>
+  </si>
+  <si>
+    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
+  </si>
+  <si>
+    <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
+  </si>
+  <si>
+    <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
+  </si>
+  <si>
+    <t>社会学</t>
+  </si>
+  <si>
+    <t>四川大学 664 &amp; 813 预测卷(一)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="10.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -478,174 +564,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,7 +973,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -902,7 +982,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -915,74 +995,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1234,265 +1251,195 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col width="12.7692307692308" customWidth="1" style="3" min="1" max="1"/>
-    <col width="86.05769230769231" customWidth="1" style="4" min="2" max="2"/>
-    <col width="11.5384615384615" customWidth="1" style="3" min="3" max="3"/>
-    <col width="9.23076923076923" customWidth="1" style="3" min="4" max="16384"/>
+    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
+    <col min="2" max="2" width="86.0576923076923" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.5384615384615" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.23076923076923" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>公共管理学</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>预测卷</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>供量/余量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>5（5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>广西大学 614 &amp; 809 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>5（5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="C4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>南京大学 661 &amp; 810 预测卷(二)</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>四川大学 666 &amp; 814 预测卷(二)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>5（3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="C7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>5（4）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>5（5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>5（5）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>社会学</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>预测卷</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>供量/余量</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>四川大学 664 &amp; 813 预测卷(一)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>5（3）</t>
-        </is>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26940" windowHeight="17120"/>
+    <workbookView windowWidth="23980" windowHeight="14320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1369,7 +1369,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3">

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23980" windowHeight="14320"/>
+    <workbookView windowWidth="22980" windowHeight="15960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,18 +41,18 @@
     <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
   </si>
   <si>
-    <t>5（4）</t>
+    <t>3（2）</t>
   </si>
   <si>
     <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
   </si>
   <si>
-    <t>5（5）</t>
-  </si>
-  <si>
     <t>广西大学 614 &amp; 809 预测卷(一)</t>
   </si>
   <si>
+    <t>3（0）</t>
+  </si>
+  <si>
     <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
   </si>
   <si>
@@ -68,10 +68,10 @@
     <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
   </si>
   <si>
-    <t>5（3）</t>
-  </si>
-  <si>
     <t>南京大学 661 &amp; 810 预测卷(二)</t>
+  </si>
+  <si>
+    <t>3（1）</t>
   </si>
   <si>
     <t>四川大学 666 &amp; 814 预测卷(二)</t>
@@ -1292,7 +1292,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1300,10 +1300,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1358,7 +1358,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1366,10 +1366,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1380,7 +1380,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1391,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1402,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1413,7 +1413,7 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1435,7 +1435,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>公共管理学</t>
   </si>
@@ -41,7 +41,7 @@
     <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
   </si>
   <si>
-    <t>3（2）</t>
+    <t>2（2）</t>
   </si>
   <si>
     <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
@@ -50,7 +50,7 @@
     <t>广西大学 614 &amp; 809 预测卷(一)</t>
   </si>
   <si>
-    <t>3（0）</t>
+    <t>2（1）</t>
   </si>
   <si>
     <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>南京大学 661 &amp; 810 预测卷(二)</t>
-  </si>
-  <si>
-    <t>3（1）</t>
   </si>
   <si>
     <t>四川大学 666 &amp; 814 预测卷(二)</t>
@@ -1336,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1347,7 +1344,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1358,7 +1355,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1369,7 +1366,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1377,10 +1374,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1388,10 +1385,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1399,7 +1396,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
@@ -1410,7 +1407,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>4</v>
@@ -1418,7 +1415,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1432,10 +1429,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22980" windowHeight="15960"/>
+    <workbookView windowWidth="20720" windowHeight="15900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>公共管理学</t>
   </si>
@@ -41,16 +41,19 @@
     <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
   </si>
   <si>
+    <t>2（1）</t>
+  </si>
+  <si>
+    <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
+  </si>
+  <si>
     <t>2（2）</t>
   </si>
   <si>
-    <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
-  </si>
-  <si>
     <t>广西大学 614 &amp; 809 预测卷(一)</t>
   </si>
   <si>
-    <t>2（1）</t>
+    <t>2（0）</t>
   </si>
   <si>
     <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
@@ -1289,7 +1292,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1297,10 +1300,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1308,10 +1311,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1319,10 +1322,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1330,10 +1333,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1341,10 +1344,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1352,10 +1355,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1363,10 +1366,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1374,10 +1377,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1385,10 +1388,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1396,10 +1399,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1407,15 +1410,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1429,10 +1432,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -1369,7 +1369,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20720" windowHeight="15900"/>
+    <workbookView windowWidth="21900" windowHeight="15900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>公共管理学</t>
   </si>
@@ -41,46 +41,43 @@
     <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
   </si>
   <si>
-    <t>2（1）</t>
+    <t>2（0）</t>
   </si>
   <si>
     <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
   </si>
   <si>
+    <t>广西大学 614 &amp; 809 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
+  </si>
+  <si>
+    <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
+  </si>
+  <si>
+    <t>南京大学 661 &amp; 810 预测卷(二)</t>
+  </si>
+  <si>
+    <t>四川大学 666 &amp; 814 预测卷(二)</t>
+  </si>
+  <si>
+    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
+  </si>
+  <si>
+    <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
+  </si>
+  <si>
     <t>2（2）</t>
-  </si>
-  <si>
-    <t>广西大学 614 &amp; 809 预测卷(一)</t>
-  </si>
-  <si>
-    <t>2（0）</t>
-  </si>
-  <si>
-    <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
-  </si>
-  <si>
-    <t>南京大学 661 &amp; 810 预测卷(二)</t>
-  </si>
-  <si>
-    <t>四川大学 666 &amp; 814 预测卷(二)</t>
-  </si>
-  <si>
-    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
-  </si>
-  <si>
-    <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
   </si>
   <si>
     <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
@@ -1292,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1300,10 +1297,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1311,10 +1308,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1322,10 +1319,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1333,10 +1330,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1344,10 +1341,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1355,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>4</v>
@@ -1366,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>4</v>
@@ -1377,10 +1374,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1388,10 +1385,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1399,10 +1396,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1410,15 +1407,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -1432,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>4</v>

--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -1,267 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21900" windowHeight="15900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21900" windowHeight="15900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
-  <si>
-    <t>公共管理学</t>
-  </si>
-  <si>
-    <t>预测卷</t>
-  </si>
-  <si>
-    <t>供量/余量</t>
-  </si>
-  <si>
-    <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
-  </si>
-  <si>
-    <t>2（0）</t>
-  </si>
-  <si>
-    <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
-  </si>
-  <si>
-    <t>广西大学 614 &amp; 809 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
-  </si>
-  <si>
-    <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
-  </si>
-  <si>
-    <t>南京大学 661 &amp; 810 预测卷(二)</t>
-  </si>
-  <si>
-    <t>四川大学 666 &amp; 814 预测卷(二)</t>
-  </si>
-  <si>
-    <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
-  </si>
-  <si>
-    <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
-  </si>
-  <si>
-    <t>2（2）</t>
-  </si>
-  <si>
-    <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
-  </si>
-  <si>
-    <t>社会学</t>
-  </si>
-  <si>
-    <t>四川大学 664 &amp; 813 预测卷(一)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="10.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -561,168 +478,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,7 +887,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -979,7 +896,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -992,11 +909,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1248,195 +1228,280 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
-    <col min="2" max="2" width="86.0576923076923" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.5384615384615" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.23076923076923" style="1" customWidth="1"/>
+    <col width="12.7692307692308" customWidth="1" style="1" min="1" max="1"/>
+    <col width="86.05769230769231" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11.5384615384615" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.23076923076923" customWidth="1" style="1" min="4" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>公共管理学</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>预测卷</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>供量/余量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>电子科技大学 631 &amp; 864 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>福建农林大学 619 &amp; 848 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>广西大学 614 &amp; 809 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>华东理工大学 623 &amp; 828社会保障 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>华东理工大学 623 &amp; 828行政管理 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>华南理工大学 626 &amp; 829 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>华南师范大学 619 &amp; 840 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>华中师范大学 709 &amp; 820 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>南京大学 661 &amp; 810 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>四川大学 666 &amp; 814 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>武汉大学 公共管理学 &amp; 公共管理研究方法 预测卷(二)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>西南财经大学 633 &amp; 803 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2（2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>浙江财经大学 611 &amp; 812 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>郑州大学 754 &amp; 818 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2（2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>社会学</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>预测卷</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>供量/余量</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1">
-        <v>1</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>4</v>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>四川大学 664 &amp; 813 预测卷(一)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2（0）</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/网页预测卷板块.xlsx
+++ b/网页预测卷板块.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21900" windowHeight="15900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19460" windowHeight="15900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1455,17 +1455,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>郑州大学 754 &amp; 818 预测卷(一)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2（2）</t>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>3（3）</t>
         </is>
       </c>
     </row>
